--- a/healthcare_forms/008_mental_health_assessment_form--healthcare_forms.xlsx
+++ b/healthcare_forms/008_mental_health_assessment_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'0',_'label':_'0'}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': '0', 'label': '0'}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'1',_'label':_'1'}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': '1', 'label': '1'}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'2',_'label':_'2'}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': '2', 'label': '2'}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'a',_'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'a', 'label': 'a'}</t>
+          <t>a</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'b',_'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'b', 'label': 'b'}</t>
+          <t>b</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'c',_'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'c', 'label': 'c'}</t>
+          <t>c</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'d',_'label':_'d'}</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'd', 'label': 'd'}</t>
+          <t>d</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'e',_'label':_'e'}</t>
+          <t>e</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'e', 'label': 'e'}</t>
+          <t>e</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'f',_'label':_'f'}</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'f', 'label': 'f'}</t>
+          <t>f</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'g',_'label':_'g'}</t>
+          <t>g</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'g', 'label': 'g'}</t>
+          <t>g</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'h',_'label':_'h'}</t>
+          <t>h</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'h', 'label': 'h'}</t>
+          <t>h</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'i',_'label':_'i'}</t>
+          <t>i</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'i', 'label': 'i'}</t>
+          <t>i</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'j',_'label':_'j'}</t>
+          <t>j</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'j', 'label': 'j'}</t>
+          <t>j</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'k',_'label':_'k'}</t>
+          <t>k</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'k', 'label': 'k'}</t>
+          <t>k</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'l',_'label':_'l'}</t>
+          <t>l</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'l', 'label': 'l'}</t>
+          <t>l</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'m',_'label':_'m'}</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'm', 'label': 'm'}</t>
+          <t>m</t>
         </is>
       </c>
     </row>
